--- a/تسعير جرد اخر شهر ٨ سنة ٢٠٢٦.xlsx
+++ b/تسعير جرد اخر شهر ٨ سنة ٢٠٢٦.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3829,10 +3829,10 @@
         <v>22.3768</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>1384</v>
+        <v>754</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>30969.49</v>
+        <v>16872.11</v>
       </c>
       <c r="L81" s="7" t="n">
         <v>0</v>
@@ -3954,10 +3954,10 @@
         <v>183.0439</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>486</v>
+        <v>708.5</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>88959.34</v>
+        <v>129686.6</v>
       </c>
       <c r="L84" s="7" t="n">
         <v>0.1094</v>
@@ -3995,10 +3995,10 @@
         <v>203.0734</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>159.5</v>
+        <v>568.8</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>32390.21</v>
+        <v>115508.15</v>
       </c>
       <c r="L85" s="7" t="n">
         <v>0.2307</v>
@@ -4036,10 +4036,10 @@
         <v>196.7193</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>177</v>
+        <v>359.5</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>34819.32</v>
+        <v>70720.59</v>
       </c>
       <c r="L86" s="7" t="n">
         <v>0.1922</v>
@@ -4077,10 +4077,10 @@
         <v>264.4955</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>570</v>
+        <v>470</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>150762.43</v>
+        <v>124312.88</v>
       </c>
       <c r="L87" s="7" t="n">
         <v>0</v>
@@ -4167,10 +4167,10 @@
         <v>165</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>524.7</v>
+        <v>494.7</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>86575.5</v>
+        <v>81625.5</v>
       </c>
       <c r="L89" s="7" t="n">
         <v>0</v>
@@ -4212,10 +4212,10 @@
         <v>206.4046</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>60.5</v>
+        <v>293</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>12487.48</v>
+        <v>60476.55</v>
       </c>
       <c r="L90" s="7" t="n">
         <v>0.2509</v>
@@ -4509,10 +4509,10 @@
         <v>119.4035</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>12179.16</v>
+        <v>9194.07</v>
       </c>
       <c r="L97" s="7" t="n">
         <v>0</v>
@@ -5093,10 +5093,10 @@
         <v>165</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>673.5</v>
+        <v>583.5</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>111127.5</v>
+        <v>96277.5</v>
       </c>
       <c r="L111" s="7" t="n">
         <v>0</v>
@@ -5318,10 +5318,10 @@
         <v>231.916</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>359.95</v>
+        <v>326.55</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>83478.16</v>
+        <v>75732.17</v>
       </c>
       <c r="L116" s="7" t="n">
         <v>0</v>
@@ -5363,10 +5363,10 @@
         <v>245.3606</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>532.95</v>
+        <v>491.35</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>130764.93</v>
+        <v>120557.93</v>
       </c>
       <c r="L117" s="7" t="n">
         <v>0</v>
@@ -5408,10 +5408,10 @@
         <v>165</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>126720</v>
+        <v>116820</v>
       </c>
       <c r="L118" s="7" t="n">
         <v>0</v>
@@ -5453,10 +5453,10 @@
         <v>203.8431</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>823.3</v>
+        <v>792.5</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>167824.02</v>
+        <v>161545.66</v>
       </c>
       <c r="L119" s="7" t="n">
         <v>0.2354</v>
@@ -5494,10 +5494,10 @@
         <v>165</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>274.8</v>
+        <v>184.8</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>45342</v>
+        <v>30492</v>
       </c>
       <c r="L120" s="7" t="n">
         <v>0</v>
@@ -5579,165 +5579,175 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>أكياس استربس ص SP</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C123" s="10" t="n"/>
-      <c r="D123" s="9" t="n"/>
-      <c r="E123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="10" t="n"/>
-      <c r="J123" s="9" t="n">
-        <v>379</v>
-      </c>
-      <c r="K123" s="9" t="n"/>
-      <c r="L123" s="11" t="n"/>
-      <c r="M123" s="8" t="inlineStr">
-        <is>
-          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
-        </is>
-      </c>
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>كراتين s.p ابيض</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="6" t="n"/>
+      <c r="D123" s="5" t="n"/>
+      <c r="E123" s="5" t="n">
+        <v>2355</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>49949.55</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>2355</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>49949.55</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="7" t="n"/>
+      <c r="M123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>كراتين s.p ابيض</t>
+          <t>علب بلاستيك شفاف</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="6" t="n"/>
-      <c r="D124" s="5" t="n"/>
+        <v>2450</v>
+      </c>
+      <c r="C124" s="6" t="n">
+        <v>2.6373</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>6461.39</v>
+      </c>
       <c r="E124" s="5" t="n">
-        <v>2355</v>
+        <v>0</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>49949.55</v>
+        <v>0</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>2355</v>
+        <v>2450</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>49949.55</v>
+        <v>6461.39</v>
       </c>
       <c r="I124" s="6" t="n">
-        <v>21.21</v>
+        <v>2.6373</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>0</v>
+        <v>1073</v>
       </c>
       <c r="K124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="7" t="n"/>
-      <c r="M124" s="4" t="inlineStr"/>
+        <v>2829.82</v>
+      </c>
+      <c r="L124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>علب بلاستيك شفاف</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="n">
-        <v>2450</v>
-      </c>
-      <c r="C125" s="6" t="n">
-        <v>2.6373</v>
-      </c>
-      <c r="D125" s="5" t="n">
-        <v>6461.39</v>
-      </c>
-      <c r="E125" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>2450</v>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>6461.39</v>
-      </c>
-      <c r="I125" s="6" t="n">
-        <v>2.6373</v>
-      </c>
-      <c r="J125" s="5" t="n">
-        <v>1073</v>
-      </c>
-      <c r="K125" s="5" t="n">
-        <v>2829.82</v>
-      </c>
-      <c r="L125" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="4" t="inlineStr">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>اكياس كفته 3ك ابوهاشم</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="10" t="n"/>
+      <c r="D125" s="9" t="n"/>
+      <c r="E125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="10" t="n"/>
+      <c r="J125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="9" t="n"/>
+      <c r="L125" s="11" t="n"/>
+      <c r="M125" s="8" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>أكياس استربس الهنا ص</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C126" s="6" t="n">
+        <v>119.5355</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>1410.52</v>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>1410.52</v>
+      </c>
+      <c r="I126" s="6" t="n">
+        <v>119.5355</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>1410.52</v>
+      </c>
+      <c r="L126" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="4" t="inlineStr">
         <is>
           <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
         </is>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>اكياس كفته 3ك ابوهاشم</t>
-        </is>
-      </c>
-      <c r="B126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" s="10" t="n"/>
-      <c r="D126" s="9" t="n"/>
-      <c r="E126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="10" t="n"/>
-      <c r="J126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" s="9" t="n"/>
-      <c r="L126" s="11" t="n"/>
-      <c r="M126" s="8" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>أكياس استربس الهنا ص</t>
+          <t>اكياس عجينه بقري 5كيلو اسبيشيال</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
-        <v>11.8</v>
+        <v>114.25</v>
       </c>
       <c r="C127" s="6" t="n">
-        <v>119.5355</v>
+        <v>115</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>1410.52</v>
+        <v>13138.75</v>
       </c>
       <c r="E127" s="5" t="n">
         <v>0</v>
@@ -5746,19 +5756,19 @@
         <v>0</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>11.8</v>
+        <v>114.25</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>1410.52</v>
+        <v>13138.75</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>119.5355</v>
+        <v>115</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>11.8</v>
+        <v>112.88</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>1410.52</v>
+        <v>12981.2</v>
       </c>
       <c r="L127" s="7" t="n">
         <v>0</v>
@@ -5772,17 +5782,17 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>اكياس عجينه بقري 5كيلو اسبيشيال</t>
+          <t>اكياس سجق اسبيشيال كيلو5</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
-        <v>114.25</v>
+        <v>128.63</v>
       </c>
       <c r="C128" s="6" t="n">
         <v>115</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>13138.75</v>
+        <v>14792.45</v>
       </c>
       <c r="E128" s="5" t="n">
         <v>0</v>
@@ -5791,19 +5801,19 @@
         <v>0</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>114.25</v>
+        <v>128.63</v>
       </c>
       <c r="H128" s="5" t="n">
-        <v>13138.75</v>
+        <v>14792.45</v>
       </c>
       <c r="I128" s="6" t="n">
         <v>115</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>112.88</v>
+        <v>128.63</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>12981.2</v>
+        <v>14792.45</v>
       </c>
       <c r="L128" s="7" t="n">
         <v>0</v>
@@ -5815,257 +5825,247 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>اكياس سجق اسبيشيال كيلو5</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="C129" s="6" t="n">
-        <v>115</v>
-      </c>
-      <c r="D129" s="5" t="n">
-        <v>14792.45</v>
-      </c>
-      <c r="E129" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" s="5" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="H129" s="5" t="n">
-        <v>14792.45</v>
-      </c>
-      <c r="I129" s="6" t="n">
-        <v>115</v>
-      </c>
-      <c r="J129" s="5" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="K129" s="5" t="n">
-        <v>14792.45</v>
-      </c>
-      <c r="L129" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" s="4" t="inlineStr">
-        <is>
-          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
-        </is>
-      </c>
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>اكياس عرض نايلون(60*90)</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="10" t="n"/>
+      <c r="D129" s="9" t="n"/>
+      <c r="E129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="10" t="n"/>
+      <c r="J129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="9" t="n"/>
+      <c r="L129" s="11" t="n"/>
+      <c r="M129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>اكياس عرض نايلون(60*90)</t>
-        </is>
-      </c>
-      <c r="B130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" s="10" t="n"/>
-      <c r="D130" s="9" t="n"/>
-      <c r="E130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="10" t="n"/>
-      <c r="J130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="9" t="n"/>
-      <c r="L130" s="11" t="n"/>
-      <c r="M130" s="8" t="inlineStr"/>
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>كراتين الهنا ازرق</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>3298</v>
+      </c>
+      <c r="C130" s="6" t="n">
+        <v>22.6926</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>74840.19</v>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>6150</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>147969</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>9448</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>222809.19</v>
+      </c>
+      <c r="I130" s="6" t="n">
+        <v>23.5827</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>7458</v>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>175879.78</v>
+      </c>
+      <c r="L130" s="7" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="M130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>كراتين الهنا ازرق</t>
+          <t>كراتين الهنا اخضر</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
-        <v>3298</v>
+        <v>2980</v>
       </c>
       <c r="C131" s="6" t="n">
-        <v>22.6926</v>
+        <v>21.6127</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>74840.19</v>
+        <v>64405.85</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>6150</v>
+        <v>0</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>147969</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>9448</v>
+        <v>2980</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>222809.19</v>
+        <v>64405.85</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>23.5827</v>
+        <v>21.6127</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>3283</v>
+        <v>2400</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>77422</v>
+        <v>51870.48</v>
       </c>
       <c r="L131" s="7" t="n">
-        <v>0.0392</v>
-      </c>
-      <c r="M131" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M131" s="4" t="inlineStr">
+        <is>
+          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>كراتين الهنا اخضر</t>
+          <t>كراتين اسبشيال احمر</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
-        <v>2980</v>
+        <v>492</v>
       </c>
       <c r="C132" s="6" t="n">
-        <v>21.6127</v>
+        <v>22.5917</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>64405.85</v>
+        <v>11115.12</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>3180</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0</v>
+        <v>74284.8</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>2980</v>
+        <v>3672</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>64405.85</v>
+        <v>85399.92</v>
       </c>
       <c r="I132" s="6" t="n">
-        <v>21.6127</v>
+        <v>23.2571</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>2505</v>
+        <v>2203</v>
       </c>
       <c r="K132" s="5" t="n">
-        <v>54139.81</v>
+        <v>51235.39</v>
       </c>
       <c r="L132" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" s="4" t="inlineStr">
-        <is>
-          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
-        </is>
-      </c>
+        <v>0.0295</v>
+      </c>
+      <c r="M132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>كراتين اسبشيال احمر</t>
+          <t>كراتين اسبشيال اسود</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
-        <v>492</v>
+        <v>2235</v>
       </c>
       <c r="C133" s="6" t="n">
-        <v>22.5917</v>
+        <v>22</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>11115.12</v>
+        <v>49170</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>3180</v>
+        <v>0</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>74284.8</v>
+        <v>0</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>3672</v>
+        <v>2235</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>85399.92</v>
+        <v>49170</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>23.2571</v>
+        <v>22</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>330</v>
+        <v>4185</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>7674.84</v>
+        <v>92070</v>
       </c>
       <c r="L133" s="7" t="n">
-        <v>0.0295</v>
-      </c>
-      <c r="M133" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M133" s="4" t="inlineStr">
+        <is>
+          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>كراتين اسبشيال اسود</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="n">
-        <v>2235</v>
-      </c>
-      <c r="C134" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="D134" s="5" t="n">
-        <v>49170</v>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>2235</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>49170</v>
-      </c>
-      <c r="I134" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="J134" s="5" t="n">
-        <v>2245</v>
-      </c>
-      <c r="K134" s="5" t="n">
-        <v>49390</v>
-      </c>
-      <c r="L134" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" s="4" t="inlineStr">
-        <is>
-          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>مذيب</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="10" t="n"/>
+      <c r="D134" s="9" t="n"/>
+      <c r="E134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="10" t="n"/>
+      <c r="J134" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K134" s="9" t="n"/>
+      <c r="L134" s="11" t="n"/>
+      <c r="M134" s="8" t="inlineStr">
+        <is>
+          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>مذيب</t>
+          <t>اكياس 40 * 60</t>
         </is>
       </c>
       <c r="B135" s="9" t="n">
@@ -6087,20 +6087,16 @@
       </c>
       <c r="I135" s="10" t="n"/>
       <c r="J135" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K135" s="9" t="n"/>
       <c r="L135" s="11" t="n"/>
-      <c r="M135" s="8" t="inlineStr">
-        <is>
-          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
-        </is>
-      </c>
+      <c r="M135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>اكياس 40 * 60</t>
+          <t>برانيك صويا</t>
         </is>
       </c>
       <c r="B136" s="9" t="n">
@@ -6131,11 +6127,11 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>برانيك صويا</t>
+          <t>برنيك برجر</t>
         </is>
       </c>
       <c r="B137" s="9" t="n">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="C137" s="10" t="n"/>
       <c r="D137" s="9" t="n"/>
@@ -6153,20 +6149,24 @@
       </c>
       <c r="I137" s="10" t="n"/>
       <c r="J137" s="9" t="n">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="K137" s="9" t="n"/>
       <c r="L137" s="11" t="n"/>
-      <c r="M137" s="8" t="inlineStr"/>
+      <c r="M137" s="8" t="inlineStr">
+        <is>
+          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>برنيك برجر</t>
+          <t>برنيك سجق</t>
         </is>
       </c>
       <c r="B138" s="9" t="n">
-        <v>442</v>
+        <v>258</v>
       </c>
       <c r="C138" s="10" t="n"/>
       <c r="D138" s="9" t="n"/>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="I138" s="10" t="n"/>
       <c r="J138" s="9" t="n">
-        <v>442</v>
+        <v>258</v>
       </c>
       <c r="K138" s="9" t="n"/>
       <c r="L138" s="11" t="n"/>
@@ -6197,29 +6197,19 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>برنيك سجق</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="n">
-        <v>258</v>
-      </c>
+          <t>أكياس استربس اسبيشيال ص</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="n"/>
       <c r="C139" s="10" t="n"/>
       <c r="D139" s="9" t="n"/>
-      <c r="E139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E139" s="9" t="n"/>
+      <c r="F139" s="9" t="n"/>
+      <c r="G139" s="9" t="n"/>
+      <c r="H139" s="9" t="n"/>
       <c r="I139" s="10" t="n"/>
       <c r="J139" s="9" t="n">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="K139" s="9" t="n"/>
       <c r="L139" s="11" t="n"/>
@@ -6230,79 +6220,89 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t>أكياس استربس اسبيشيال ص</t>
-        </is>
-      </c>
-      <c r="B140" s="9" t="n"/>
-      <c r="C140" s="10" t="n"/>
-      <c r="D140" s="9" t="n"/>
-      <c r="E140" s="9" t="n"/>
-      <c r="F140" s="9" t="n"/>
-      <c r="G140" s="9" t="n"/>
-      <c r="H140" s="9" t="n"/>
-      <c r="I140" s="10" t="n"/>
-      <c r="J140" s="9" t="n">
-        <v>82</v>
-      </c>
-      <c r="K140" s="9" t="n"/>
-      <c r="L140" s="11" t="n"/>
-      <c r="M140" s="8" t="inlineStr">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>أكياس بانيه الهنا 5 ك</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>2475</v>
+      </c>
+      <c r="L140" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>فلاتر</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="10" t="n"/>
+      <c r="D141" s="9" t="n"/>
+      <c r="E141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="10" t="n"/>
+      <c r="J141" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K141" s="9" t="n"/>
+      <c r="L141" s="11" t="n"/>
+      <c r="M141" s="8" t="inlineStr">
         <is>
           <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>أكياس بانيه الهنا 5 ك</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" s="6" t="n">
-        <v>165</v>
-      </c>
-      <c r="D141" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="6" t="n">
-        <v>165</v>
-      </c>
-      <c r="J141" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K141" s="5" t="n">
-        <v>2475</v>
-      </c>
-      <c r="L141" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" s="4" t="inlineStr">
-        <is>
-          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>فلاتر</t>
+          <t>استطوانة فريون</t>
         </is>
       </c>
       <c r="B142" s="9" t="n">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="I142" s="10" t="n"/>
       <c r="J142" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K142" s="9" t="n"/>
       <c r="L142" s="11" t="n"/>
@@ -6337,7 +6337,7 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>استطوانة فريون</t>
+          <t>فلتر خاص بالثلاجة</t>
         </is>
       </c>
       <c r="B143" s="9" t="n">
@@ -6370,83 +6370,83 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>فلتر خاص بالثلاجة</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" s="10" t="n"/>
-      <c r="D144" s="9" t="n"/>
-      <c r="E144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" s="10" t="n"/>
-      <c r="J144" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K144" s="9" t="n"/>
-      <c r="L144" s="11" t="n"/>
-      <c r="M144" s="8" t="inlineStr">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>زيت سيارات</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="5" t="n"/>
+      <c r="E144" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I144" s="6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>2700</v>
+      </c>
+      <c r="L144" s="7" t="n"/>
+      <c r="M144" s="4" t="inlineStr">
+        <is>
+          <t>الوحدة: عبوة 5 كجم (سعر العبوة وليس الكجم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>حشوة زيت</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" s="10" t="n"/>
+      <c r="D145" s="9" t="n"/>
+      <c r="E145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="10" t="n"/>
+      <c r="J145" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K145" s="9" t="n"/>
+      <c r="L145" s="11" t="n"/>
+      <c r="M145" s="8" t="inlineStr">
         <is>
           <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>زيت سيارات</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C145" s="6" t="n"/>
-      <c r="D145" s="5" t="n"/>
-      <c r="E145" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>12150</v>
-      </c>
-      <c r="G145" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H145" s="5" t="n">
-        <v>12150</v>
-      </c>
-      <c r="I145" s="6" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J145" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K145" s="5" t="n">
-        <v>2700</v>
-      </c>
-      <c r="L145" s="7" t="n"/>
-      <c r="M145" s="4" t="inlineStr">
-        <is>
-          <t>الوحدة: عبوة 5 كجم (سعر العبوة وليس الكجم)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>حشوة زيت</t>
+          <t>خام عجينة برجر  أبو هاشم</t>
         </is>
       </c>
       <c r="B146" s="9" t="n">
@@ -6468,20 +6468,16 @@
       </c>
       <c r="I146" s="10" t="n"/>
       <c r="J146" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K146" s="9" t="n"/>
       <c r="L146" s="11" t="n"/>
-      <c r="M146" s="8" t="inlineStr">
-        <is>
-          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
-        </is>
-      </c>
+      <c r="M146" s="8" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة برجر  أبو هاشم</t>
+          <t>خام عجينه بقري اسبيشيال</t>
         </is>
       </c>
       <c r="B147" s="9" t="n">
@@ -6512,7 +6508,7 @@
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>خام عجينه بقري اسبيشيال</t>
+          <t>خام عجينة برجر  الهنا</t>
         </is>
       </c>
       <c r="B148" s="9" t="n">
@@ -6543,7 +6539,7 @@
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة برجر  الهنا</t>
+          <t>خام عجينة كفته الهنا</t>
         </is>
       </c>
       <c r="B149" s="9" t="n">
@@ -6574,7 +6570,7 @@
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة كفته الهنا</t>
+          <t>خام عجينة سجق الهنا</t>
         </is>
       </c>
       <c r="B150" s="9" t="n">
@@ -6605,7 +6601,7 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة سجق الهنا</t>
+          <t>خام عجينة برجر اسبيشيال</t>
         </is>
       </c>
       <c r="B151" s="9" t="n">
@@ -6636,79 +6632,48 @@
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة برجر اسبيشيال</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="n">
-        <v>0</v>
-      </c>
+          <t>فلتر هواء</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="n"/>
       <c r="C152" s="10" t="n"/>
       <c r="D152" s="9" t="n"/>
-      <c r="E152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E152" s="9" t="n"/>
+      <c r="F152" s="9" t="n"/>
+      <c r="G152" s="9" t="n"/>
+      <c r="H152" s="9" t="n"/>
       <c r="I152" s="10" t="n"/>
       <c r="J152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K152" s="9" t="n"/>
       <c r="L152" s="11" t="n"/>
-      <c r="M152" s="8" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>فلتر هواء</t>
-        </is>
-      </c>
-      <c r="B153" s="9" t="n"/>
-      <c r="C153" s="10" t="n"/>
-      <c r="D153" s="9" t="n"/>
-      <c r="E153" s="9" t="n"/>
-      <c r="F153" s="9" t="n"/>
-      <c r="G153" s="9" t="n"/>
-      <c r="H153" s="9" t="n"/>
-      <c r="I153" s="10" t="n"/>
-      <c r="J153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" s="9" t="n"/>
-      <c r="L153" s="11" t="n"/>
-      <c r="M153" s="8" t="inlineStr">
+      <c r="M152" s="8" t="inlineStr">
         <is>
           <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="12" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="12" t="inlineStr">
         <is>
           <t>إجمالى قيمة مخزون الخامات آخر أغسطس 2026 (الأصناف المُسعّرة)</t>
         </is>
       </c>
-      <c r="B155" s="12" t="n"/>
-      <c r="C155" s="12" t="n"/>
-      <c r="D155" s="12" t="n"/>
-      <c r="E155" s="12" t="n"/>
-      <c r="F155" s="12" t="n"/>
-      <c r="G155" s="12" t="n"/>
-      <c r="H155" s="12" t="n"/>
-      <c r="I155" s="12" t="n"/>
-      <c r="J155" s="12" t="n"/>
-      <c r="K155" s="12" t="n">
-        <v>2699854.27</v>
-      </c>
-      <c r="L155" s="12" t="n"/>
-      <c r="M155" s="12" t="n"/>
+      <c r="B154" s="12" t="n"/>
+      <c r="C154" s="12" t="n"/>
+      <c r="D154" s="12" t="n"/>
+      <c r="E154" s="12" t="n"/>
+      <c r="F154" s="12" t="n"/>
+      <c r="G154" s="12" t="n"/>
+      <c r="H154" s="12" t="n"/>
+      <c r="I154" s="12" t="n"/>
+      <c r="J154" s="12" t="n"/>
+      <c r="K154" s="12" t="n">
+        <v>2977705.44</v>
+      </c>
+      <c r="L154" s="12" t="n"/>
+      <c r="M154" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15646,7 +15611,7 @@
       <c r="D108" s="17" t="n"/>
       <c r="E108" s="17" t="n"/>
       <c r="F108" s="17" t="n">
-        <v>3135454.56</v>
+        <v>3413305.73</v>
       </c>
       <c r="G108" s="17" t="n"/>
     </row>
@@ -15971,7 +15936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -16227,77 +16192,77 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>أكياس استربس ص SP</t>
+          <t>برنيك سجق</t>
         </is>
       </c>
       <c r="B26" s="22" t="n">
-        <v>379</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>برنيك سجق</t>
+          <t>أكياس استربس اسبيشيال ص</t>
         </is>
       </c>
       <c r="B27" s="22" t="n">
-        <v>258</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>أكياس استربس اسبيشيال ص</t>
+          <t>طبق مسطح 1/2 شفاف</t>
         </is>
       </c>
       <c r="B28" s="22" t="n">
-        <v>82</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>طبق مسطح 1/2 شفاف</t>
+          <t>فلاتر</t>
         </is>
       </c>
       <c r="B29" s="22" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>فلاتر</t>
+          <t>حشوة زيت</t>
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>حشوة زيت</t>
+          <t>مذيب</t>
         </is>
       </c>
       <c r="B31" s="22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>مذيب</t>
+          <t>مزيل لماكينة التغليف</t>
         </is>
       </c>
       <c r="B32" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>مزيل لماكينة التغليف</t>
+          <t>استطوانة فريون</t>
         </is>
       </c>
       <c r="B33" s="22" t="n">
@@ -16307,20 +16272,10 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>استطوانة فريون</t>
+          <t>فلتر خاص بالثلاجة</t>
         </is>
       </c>
       <c r="B34" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>فلتر خاص بالثلاجة</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="n">
         <v>1</v>
       </c>
     </row>

--- a/تسعير جرد اخر شهر ٨ سنة ٢٠٢٦.xlsx
+++ b/تسعير جرد اخر شهر ٨ سنة ٢٠٢٦.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -692,10 +692,10 @@
         <v>25.0724</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1249.55</v>
+        <v>1249.3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>31329.22</v>
+        <v>31322.95</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>فلانك</t>
+          <t>فلانك + مجمل رصيد اللحمة بالنفق</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -1243,7 +1243,11 @@
       <c r="L19" s="7" t="n">
         <v>-0.0074</v>
       </c>
-      <c r="M19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>أُعيدت تسميته بجرد أغسطس؛ رصيد أول المدة مأخوذ من «فلانك» بجرد يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3680,7 +3684,7 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>كروت كبده شرائح 350</t>
+          <t>كروت كبده علب 350</t>
         </is>
       </c>
       <c r="B78" s="9" t="n">
@@ -4960,7 +4964,7 @@
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>كروت مفروم صويا ازرق 350</t>
+          <t>كروت استربس</t>
         </is>
       </c>
       <c r="B108" s="9" t="n">
@@ -5153,64 +5157,44 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>اكياس برجر ابوهاشم 1ك</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="C113" s="6" t="n">
-        <v>165</v>
-      </c>
-      <c r="D113" s="5" t="n">
-        <v>8250</v>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>8250</v>
-      </c>
-      <c r="I113" s="6" t="n">
-        <v>165</v>
-      </c>
-      <c r="J113" s="5" t="n">
-        <v>2036</v>
-      </c>
-      <c r="K113" s="5" t="n">
-        <v>335940</v>
-      </c>
-      <c r="L113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="4" t="inlineStr">
-        <is>
-          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>كروت برجر أبو هاشم</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="10" t="n"/>
+      <c r="D113" s="9" t="n"/>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="9" t="n"/>
+      <c r="H113" s="9" t="n"/>
+      <c r="I113" s="10" t="n"/>
+      <c r="J113" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K113" s="9" t="n"/>
+      <c r="L113" s="11" t="n"/>
+      <c r="M113" s="8" t="inlineStr">
+        <is>
+          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>اكياس سجق s.p صغير</t>
+          <t>اكياس برجر ابوهاشم 1ك</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="C114" s="6" t="n">
         <v>165</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>33000</v>
+        <v>8250</v>
       </c>
       <c r="E114" s="5" t="n">
         <v>0</v>
@@ -5219,19 +5203,19 @@
         <v>0</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>33000</v>
+        <v>8250</v>
       </c>
       <c r="I114" s="6" t="n">
         <v>165</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>146.13</v>
+        <v>42.13</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>24111.45</v>
+        <v>6951.45</v>
       </c>
       <c r="L114" s="7" t="n">
         <v>0</v>
@@ -5245,17 +5229,17 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>اكياس سجق s.p كبير</t>
+          <t>اكياس سجق s.p صغير</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>366</v>
+        <v>200</v>
       </c>
       <c r="C115" s="6" t="n">
         <v>165</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>60390</v>
+        <v>33000</v>
       </c>
       <c r="E115" s="5" t="n">
         <v>0</v>
@@ -5264,19 +5248,19 @@
         <v>0</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>366</v>
+        <v>200</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>60390</v>
+        <v>33000</v>
       </c>
       <c r="I115" s="6" t="n">
         <v>165</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>288.3</v>
+        <v>188.3</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>47569.5</v>
+        <v>31069.5</v>
       </c>
       <c r="L115" s="7" t="n">
         <v>0</v>
@@ -5290,17 +5274,17 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>اكياس برجر s.p صغير</t>
+          <t>اكياس سجق s.p كبير</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>288.35</v>
+        <v>366</v>
       </c>
       <c r="C116" s="6" t="n">
-        <v>231.916</v>
+        <v>165</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>66872.98</v>
+        <v>60390</v>
       </c>
       <c r="E116" s="5" t="n">
         <v>0</v>
@@ -5309,19 +5293,19 @@
         <v>0</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>288.35</v>
+        <v>366</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>66872.98</v>
+        <v>60390</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>231.916</v>
+        <v>165</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>326.55</v>
+        <v>360</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>75732.17</v>
+        <v>59400</v>
       </c>
       <c r="L116" s="7" t="n">
         <v>0</v>
@@ -5335,17 +5319,17 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>اكياس كفته s.p صغير</t>
+          <t>اكياس برجر s.p صغير</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
-        <v>479.15</v>
+        <v>288.35</v>
       </c>
       <c r="C117" s="6" t="n">
-        <v>245.3606</v>
+        <v>231.916</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>117564.53</v>
+        <v>66872.98</v>
       </c>
       <c r="E117" s="5" t="n">
         <v>0</v>
@@ -5354,19 +5338,19 @@
         <v>0</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>479.15</v>
+        <v>288.35</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>117564.53</v>
+        <v>66872.98</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>245.3606</v>
+        <v>231.916</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>491.35</v>
+        <v>260.15</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>120557.93</v>
+        <v>60332.95</v>
       </c>
       <c r="L117" s="7" t="n">
         <v>0</v>
@@ -5380,17 +5364,17 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>اكياس كفته s.p كبير</t>
+          <t>اكياس كفته s.p صغير</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
-        <v>800.5</v>
+        <v>479.15</v>
       </c>
       <c r="C118" s="6" t="n">
-        <v>165</v>
+        <v>245.3606</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>132082.5</v>
+        <v>117564.53</v>
       </c>
       <c r="E118" s="5" t="n">
         <v>0</v>
@@ -5399,19 +5383,19 @@
         <v>0</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>800.5</v>
+        <v>479.15</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>132082.5</v>
+        <v>117564.53</v>
       </c>
       <c r="I118" s="6" t="n">
-        <v>165</v>
+        <v>245.3606</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>708</v>
+        <v>456.35</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>116820</v>
+        <v>111970.31</v>
       </c>
       <c r="L118" s="7" t="n">
         <v>0</v>
@@ -5425,132 +5409,142 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>اكياس برجر s.p كبير</t>
+          <t>اكياس كفته s.p كبير</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>161.2</v>
+        <v>800.5</v>
       </c>
       <c r="C119" s="6" t="n">
         <v>165</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>26598</v>
+        <v>132082.5</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>683.8</v>
+        <v>0</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>145649.4</v>
+        <v>0</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>845</v>
+        <v>800.5</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>172247.4</v>
+        <v>132082.5</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>203.8431</v>
+        <v>165</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>792.5</v>
+        <v>709</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>161545.66</v>
+        <v>116985</v>
       </c>
       <c r="L119" s="7" t="n">
-        <v>0.2354</v>
-      </c>
-      <c r="M119" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="4" t="inlineStr">
+        <is>
+          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>اكياس بانيه s.p</t>
+          <t>اكياس برجر s.p كبير</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>192</v>
+        <v>161.2</v>
       </c>
       <c r="C120" s="6" t="n">
         <v>165</v>
       </c>
       <c r="D120" s="5" t="n">
+        <v>26598</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>683.8</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>145649.4</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>845</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>172247.4</v>
+      </c>
+      <c r="I120" s="6" t="n">
+        <v>203.8431</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>795.3</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>162116.42</v>
+      </c>
+      <c r="L120" s="7" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="M120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>اكياس بانيه s.p</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="C121" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="D121" s="5" t="n">
         <v>31680</v>
       </c>
-      <c r="E120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="5" t="n">
+      <c r="E121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="5" t="n">
         <v>192</v>
       </c>
-      <c r="H120" s="5" t="n">
+      <c r="H121" s="5" t="n">
         <v>31680</v>
       </c>
-      <c r="I120" s="6" t="n">
+      <c r="I121" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="J120" s="5" t="n">
-        <v>184.8</v>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>30492</v>
-      </c>
-      <c r="L120" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="4" t="inlineStr">
+      <c r="J121" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>29205</v>
+      </c>
+      <c r="L121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="4" t="inlineStr">
         <is>
           <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>طبق مسطح 1/2 شفاف</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="n">
-        <v>1450</v>
-      </c>
-      <c r="C121" s="10" t="n"/>
-      <c r="D121" s="9" t="n"/>
-      <c r="E121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" s="10" t="n"/>
-      <c r="J121" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="K121" s="9" t="n"/>
-      <c r="L121" s="11" t="n"/>
-      <c r="M121" s="8" t="inlineStr">
-        <is>
-          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>طبق مسطح 3/4شفاف</t>
+          <t>طبق مسطح 1/2 شفاف</t>
         </is>
       </c>
       <c r="B122" s="9" t="n">
-        <v>1406</v>
+        <v>1450</v>
       </c>
       <c r="C122" s="10" t="n"/>
       <c r="D122" s="9" t="n"/>
@@ -5579,130 +5573,104 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>طبق مسطح 1 ك شفاف</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="n"/>
+      <c r="C123" s="10" t="n"/>
+      <c r="D123" s="9" t="n"/>
+      <c r="E123" s="9" t="n"/>
+      <c r="F123" s="9" t="n"/>
+      <c r="G123" s="9" t="n"/>
+      <c r="H123" s="9" t="n"/>
+      <c r="I123" s="10" t="n"/>
+      <c r="J123" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="K123" s="9" t="n"/>
+      <c r="L123" s="11" t="n"/>
+      <c r="M123" s="8" t="inlineStr">
+        <is>
+          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>أكياس استربس وبانيه شفاف ص</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="n"/>
+      <c r="C124" s="10" t="n"/>
+      <c r="D124" s="9" t="n"/>
+      <c r="E124" s="9" t="n"/>
+      <c r="F124" s="9" t="n"/>
+      <c r="G124" s="9" t="n"/>
+      <c r="H124" s="9" t="n"/>
+      <c r="I124" s="10" t="n"/>
+      <c r="J124" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="9" t="n"/>
+      <c r="L124" s="11" t="n"/>
+      <c r="M124" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>كراتين s.p ابيض</t>
         </is>
       </c>
-      <c r="B123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="6" t="n"/>
-      <c r="D123" s="5" t="n"/>
-      <c r="E123" s="5" t="n">
+      <c r="B125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="5" t="n"/>
+      <c r="E125" s="5" t="n">
         <v>2355</v>
       </c>
-      <c r="F123" s="5" t="n">
+      <c r="F125" s="5" t="n">
         <v>49949.55</v>
       </c>
-      <c r="G123" s="5" t="n">
+      <c r="G125" s="5" t="n">
         <v>2355</v>
       </c>
-      <c r="H123" s="5" t="n">
+      <c r="H125" s="5" t="n">
         <v>49949.55</v>
       </c>
-      <c r="I123" s="6" t="n">
+      <c r="I125" s="6" t="n">
         <v>21.21</v>
       </c>
-      <c r="J123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="7" t="n"/>
-      <c r="M123" s="4" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>علب بلاستيك شفاف</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="n">
-        <v>2450</v>
-      </c>
-      <c r="C124" s="6" t="n">
-        <v>2.6373</v>
-      </c>
-      <c r="D124" s="5" t="n">
-        <v>6461.39</v>
-      </c>
-      <c r="E124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>2450</v>
-      </c>
-      <c r="H124" s="5" t="n">
-        <v>6461.39</v>
-      </c>
-      <c r="I124" s="6" t="n">
-        <v>2.6373</v>
-      </c>
-      <c r="J124" s="5" t="n">
-        <v>1073</v>
-      </c>
-      <c r="K124" s="5" t="n">
-        <v>2829.82</v>
-      </c>
-      <c r="L124" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="4" t="inlineStr">
-        <is>
-          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t>اكياس كفته 3ك ابوهاشم</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" s="10" t="n"/>
-      <c r="D125" s="9" t="n"/>
-      <c r="E125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="10" t="n"/>
-      <c r="J125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="9" t="n"/>
-      <c r="L125" s="11" t="n"/>
-      <c r="M125" s="8" t="inlineStr"/>
+      <c r="J125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="7" t="n"/>
+      <c r="M125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>أكياس استربس الهنا ص</t>
+          <t>علب بلاستيك شفاف</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
-        <v>11.8</v>
+        <v>2450</v>
       </c>
       <c r="C126" s="6" t="n">
-        <v>119.5355</v>
+        <v>2.6373</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>1410.52</v>
+        <v>6461.39</v>
       </c>
       <c r="E126" s="5" t="n">
         <v>0</v>
@@ -5711,19 +5679,19 @@
         <v>0</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>11.8</v>
+        <v>2450</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>1410.52</v>
+        <v>6461.39</v>
       </c>
       <c r="I126" s="6" t="n">
-        <v>119.5355</v>
+        <v>2.6373</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>11.8</v>
+        <v>1073</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>1410.52</v>
+        <v>2829.82</v>
       </c>
       <c r="L126" s="7" t="n">
         <v>0</v>
@@ -5735,368 +5703,378 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>اكياس عجينه بقري 5كيلو اسبيشيال</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="n">
-        <v>114.25</v>
-      </c>
-      <c r="C127" s="6" t="n">
-        <v>115</v>
-      </c>
-      <c r="D127" s="5" t="n">
-        <v>13138.75</v>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" s="5" t="n">
-        <v>114.25</v>
-      </c>
-      <c r="H127" s="5" t="n">
-        <v>13138.75</v>
-      </c>
-      <c r="I127" s="6" t="n">
-        <v>115</v>
-      </c>
-      <c r="J127" s="5" t="n">
-        <v>112.88</v>
-      </c>
-      <c r="K127" s="5" t="n">
-        <v>12981.2</v>
-      </c>
-      <c r="L127" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="4" t="inlineStr">
-        <is>
-          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
-        </is>
-      </c>
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>اكياس كفته 3ك ابوهاشم</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="10" t="n"/>
+      <c r="D127" s="9" t="n"/>
+      <c r="E127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="10" t="n"/>
+      <c r="J127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="9" t="n"/>
+      <c r="L127" s="11" t="n"/>
+      <c r="M127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>اكياس سجق اسبيشيال كيلو5</t>
+          <t>أكياس استربس الهنا ص</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
-        <v>128.63</v>
+        <v>11.8</v>
       </c>
       <c r="C128" s="6" t="n">
+        <v>119.5355</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>1410.52</v>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>1410.52</v>
+      </c>
+      <c r="I128" s="6" t="n">
+        <v>119.5355</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>1410.52</v>
+      </c>
+      <c r="L128" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="4" t="inlineStr">
+        <is>
+          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>اكياس عجينه بقري 5كيلو اسبيشيال</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="C129" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="D128" s="5" t="n">
-        <v>14792.45</v>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="5" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="H128" s="5" t="n">
-        <v>14792.45</v>
-      </c>
-      <c r="I128" s="6" t="n">
+      <c r="D129" s="5" t="n">
+        <v>13138.75</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>13138.75</v>
+      </c>
+      <c r="I129" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="J128" s="5" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>14792.45</v>
-      </c>
-      <c r="L128" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" s="4" t="inlineStr">
+      <c r="J129" s="5" t="n">
+        <v>112.88</v>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>12981.2</v>
+      </c>
+      <c r="L129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="4" t="inlineStr">
         <is>
           <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
         </is>
       </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t>اكياس عرض نايلون(60*90)</t>
-        </is>
-      </c>
-      <c r="B129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" s="10" t="n"/>
-      <c r="D129" s="9" t="n"/>
-      <c r="E129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="10" t="n"/>
-      <c r="J129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="9" t="n"/>
-      <c r="L129" s="11" t="n"/>
-      <c r="M129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>كراتين الهنا ازرق</t>
+          <t>اكياس سجق اسبيشيال كيلو5</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
-        <v>3298</v>
+        <v>128.63</v>
       </c>
       <c r="C130" s="6" t="n">
-        <v>22.6926</v>
+        <v>115</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>74840.19</v>
+        <v>14792.45</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>6150</v>
+        <v>0</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>147969</v>
+        <v>0</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>9448</v>
+        <v>128.63</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>222809.19</v>
+        <v>14792.45</v>
       </c>
       <c r="I130" s="6" t="n">
-        <v>23.5827</v>
+        <v>115</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>7458</v>
+        <v>128.63</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>175879.78</v>
+        <v>14792.45</v>
       </c>
       <c r="L130" s="7" t="n">
-        <v>0.0392</v>
-      </c>
-      <c r="M130" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M130" s="4" t="inlineStr">
+        <is>
+          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>كراتين الهنا اخضر</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="n">
-        <v>2980</v>
-      </c>
-      <c r="C131" s="6" t="n">
-        <v>21.6127</v>
-      </c>
-      <c r="D131" s="5" t="n">
-        <v>64405.85</v>
-      </c>
-      <c r="E131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>2980</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>64405.85</v>
-      </c>
-      <c r="I131" s="6" t="n">
-        <v>21.6127</v>
-      </c>
-      <c r="J131" s="5" t="n">
-        <v>2400</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>51870.48</v>
-      </c>
-      <c r="L131" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" s="4" t="inlineStr">
-        <is>
-          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
-        </is>
-      </c>
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>اكياس عرض نايلون(60*90)</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="10" t="n"/>
+      <c r="D131" s="9" t="n"/>
+      <c r="E131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="10" t="n"/>
+      <c r="J131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="9" t="n"/>
+      <c r="L131" s="11" t="n"/>
+      <c r="M131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>كراتين اسبشيال احمر</t>
+          <t>كراتين الهنا ازرق</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
-        <v>492</v>
+        <v>3298</v>
       </c>
       <c r="C132" s="6" t="n">
-        <v>22.5917</v>
+        <v>22.6926</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>11115.12</v>
+        <v>74840.19</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3180</v>
+        <v>6150</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>74284.8</v>
+        <v>147969</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>3672</v>
+        <v>9448</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>85399.92</v>
+        <v>222809.19</v>
       </c>
       <c r="I132" s="6" t="n">
-        <v>23.2571</v>
+        <v>23.5827</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>2203</v>
+        <v>7458</v>
       </c>
       <c r="K132" s="5" t="n">
-        <v>51235.39</v>
+        <v>175879.78</v>
       </c>
       <c r="L132" s="7" t="n">
-        <v>0.0295</v>
+        <v>0.0392</v>
       </c>
       <c r="M132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
+          <t>كراتين الهنا اخضر</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>2980</v>
+      </c>
+      <c r="C133" s="6" t="n">
+        <v>21.6127</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>64405.85</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>64405.85</v>
+      </c>
+      <c r="I133" s="6" t="n">
+        <v>21.6127</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>51870.48</v>
+      </c>
+      <c r="L133" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="4" t="inlineStr">
+        <is>
+          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>كراتين اسبشيال احمر</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>492</v>
+      </c>
+      <c r="C134" s="6" t="n">
+        <v>22.5917</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>11115.12</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>3180</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>74284.8</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>3672</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>85399.92</v>
+      </c>
+      <c r="I134" s="6" t="n">
+        <v>23.2571</v>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>2203</v>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>51235.39</v>
+      </c>
+      <c r="L134" s="7" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="M134" s="4" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
           <t>كراتين اسبشيال اسود</t>
         </is>
       </c>
-      <c r="B133" s="5" t="n">
+      <c r="B135" s="5" t="n">
         <v>2235</v>
       </c>
-      <c r="C133" s="6" t="n">
+      <c r="C135" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="D133" s="5" t="n">
+      <c r="D135" s="5" t="n">
         <v>49170</v>
       </c>
-      <c r="E133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="5" t="n">
+      <c r="E135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="5" t="n">
         <v>2235</v>
       </c>
-      <c r="H133" s="5" t="n">
+      <c r="H135" s="5" t="n">
         <v>49170</v>
       </c>
-      <c r="I133" s="6" t="n">
+      <c r="I135" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="J133" s="5" t="n">
+      <c r="J135" s="5" t="n">
         <v>4185</v>
       </c>
-      <c r="K133" s="5" t="n">
+      <c r="K135" s="5" t="n">
         <v>92070</v>
       </c>
-      <c r="L133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" s="4" t="inlineStr">
+      <c r="L135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="4" t="inlineStr">
         <is>
           <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
         </is>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="8" t="inlineStr">
-        <is>
-          <t>مذيب</t>
-        </is>
-      </c>
-      <c r="B134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C134" s="10" t="n"/>
-      <c r="D134" s="9" t="n"/>
-      <c r="E134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="10" t="n"/>
-      <c r="J134" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K134" s="9" t="n"/>
-      <c r="L134" s="11" t="n"/>
-      <c r="M134" s="8" t="inlineStr">
-        <is>
-          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="8" t="inlineStr">
-        <is>
-          <t>اكياس 40 * 60</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" s="10" t="n"/>
-      <c r="D135" s="9" t="n"/>
-      <c r="E135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="10" t="n"/>
-      <c r="J135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="9" t="n"/>
-      <c r="L135" s="11" t="n"/>
-      <c r="M135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>برانيك صويا</t>
+          <t>مذيب</t>
         </is>
       </c>
       <c r="B136" s="9" t="n">
@@ -6127,11 +6105,11 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>برنيك برجر</t>
+          <t>اكياس 40 * 60</t>
         </is>
       </c>
       <c r="B137" s="9" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="C137" s="10" t="n"/>
       <c r="D137" s="9" t="n"/>
@@ -6149,24 +6127,20 @@
       </c>
       <c r="I137" s="10" t="n"/>
       <c r="J137" s="9" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="K137" s="9" t="n"/>
       <c r="L137" s="11" t="n"/>
-      <c r="M137" s="8" t="inlineStr">
-        <is>
-          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
-        </is>
-      </c>
+      <c r="M137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>برنيك سجق</t>
+          <t>برانيك صويا</t>
         </is>
       </c>
       <c r="B138" s="9" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="C138" s="10" t="n"/>
       <c r="D138" s="9" t="n"/>
@@ -6184,7 +6158,7 @@
       </c>
       <c r="I138" s="10" t="n"/>
       <c r="J138" s="9" t="n">
-        <v>258</v>
+        <v>442</v>
       </c>
       <c r="K138" s="9" t="n"/>
       <c r="L138" s="11" t="n"/>
@@ -6197,19 +6171,29 @@
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>أكياس استربس اسبيشيال ص</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="n"/>
+          <t>برنيك برجر</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="n">
+        <v>442</v>
+      </c>
       <c r="C139" s="10" t="n"/>
       <c r="D139" s="9" t="n"/>
-      <c r="E139" s="9" t="n"/>
-      <c r="F139" s="9" t="n"/>
-      <c r="G139" s="9" t="n"/>
-      <c r="H139" s="9" t="n"/>
+      <c r="E139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="I139" s="10" t="n"/>
       <c r="J139" s="9" t="n">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="K139" s="9" t="n"/>
       <c r="L139" s="11" t="n"/>
@@ -6220,111 +6204,97 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>أكياس بانيه الهنا 5 ك</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" s="6" t="n">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>برنيك سجق</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="n">
+        <v>258</v>
+      </c>
+      <c r="C140" s="10" t="n"/>
+      <c r="D140" s="9" t="n"/>
+      <c r="E140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="10" t="n"/>
+      <c r="J140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" s="9" t="n"/>
+      <c r="L140" s="11" t="n"/>
+      <c r="M140" s="8" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>أكياس بانيه استربس 5 الهنا</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="D140" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" s="6" t="n">
+      <c r="D141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="J140" s="5" t="n">
+      <c r="J141" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="K140" s="5" t="n">
+      <c r="K141" s="5" t="n">
         <v>2475</v>
       </c>
-      <c r="L140" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" s="4" t="inlineStr">
-        <is>
-          <t>لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t>فلاتر</t>
-        </is>
-      </c>
-      <c r="B141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" s="10" t="n"/>
-      <c r="D141" s="9" t="n"/>
-      <c r="E141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="10" t="n"/>
-      <c r="J141" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="K141" s="9" t="n"/>
-      <c r="L141" s="11" t="n"/>
-      <c r="M141" s="8" t="inlineStr">
-        <is>
-          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
+      <c r="L141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="4" t="inlineStr">
+        <is>
+          <t>أُعيدت تسميته بجرد أغسطس؛ رصيد أول المدة مأخوذ من «أكياس بانيه الهنا 5 ك» بجرد يوليو — لا مشتريات فى أغسطس ⇒ السعر ثابت كما فى يوليو</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>استطوانة فريون</t>
-        </is>
-      </c>
-      <c r="B142" s="9" t="n">
-        <v>0</v>
-      </c>
+          <t>أكياس استربس اسبيشيال ص</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="n"/>
       <c r="C142" s="10" t="n"/>
       <c r="D142" s="9" t="n"/>
-      <c r="E142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="9" t="n"/>
+      <c r="G142" s="9" t="n"/>
+      <c r="H142" s="9" t="n"/>
       <c r="I142" s="10" t="n"/>
       <c r="J142" s="9" t="n">
-        <v>1</v>
+        <v>82.5</v>
       </c>
       <c r="K142" s="9" t="n"/>
       <c r="L142" s="11" t="n"/>
@@ -6337,81 +6307,57 @@
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>فلتر خاص بالثلاجة</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="n">
-        <v>0</v>
-      </c>
+          <t>خام عجينة سجق أبو هاشم</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="n"/>
       <c r="C143" s="10" t="n"/>
       <c r="D143" s="9" t="n"/>
-      <c r="E143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E143" s="9" t="n"/>
+      <c r="F143" s="9" t="n"/>
+      <c r="G143" s="9" t="n"/>
+      <c r="H143" s="9" t="n"/>
       <c r="I143" s="10" t="n"/>
       <c r="J143" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K143" s="9" t="n"/>
       <c r="L143" s="11" t="n"/>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>زيت سيارات</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" s="6" t="n"/>
-      <c r="D144" s="5" t="n"/>
-      <c r="E144" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>12150</v>
-      </c>
-      <c r="G144" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H144" s="5" t="n">
-        <v>12150</v>
-      </c>
-      <c r="I144" s="6" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J144" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K144" s="5" t="n">
-        <v>2700</v>
-      </c>
-      <c r="L144" s="7" t="n"/>
-      <c r="M144" s="4" t="inlineStr">
-        <is>
-          <t>الوحدة: عبوة 5 كجم (سعر العبوة وليس الكجم)</t>
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>خام عجينة كفته أبو هاشم</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="9" t="n"/>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="n"/>
+      <c r="G144" s="9" t="n"/>
+      <c r="H144" s="9" t="n"/>
+      <c r="I144" s="10" t="n"/>
+      <c r="J144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" s="9" t="n"/>
+      <c r="L144" s="11" t="n"/>
+      <c r="M144" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t>حشوة زيت</t>
+          <t>خام عجينة برجر  أبو هاشم</t>
         </is>
       </c>
       <c r="B145" s="9" t="n">
@@ -6433,51 +6379,41 @@
       </c>
       <c r="I145" s="10" t="n"/>
       <c r="J145" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K145" s="9" t="n"/>
       <c r="L145" s="11" t="n"/>
-      <c r="M145" s="8" t="inlineStr">
-        <is>
-          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
-        </is>
-      </c>
+      <c r="M145" s="8" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة برجر  أبو هاشم</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="n">
-        <v>0</v>
-      </c>
+          <t>خام مفروم صافى 5ك</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="n"/>
       <c r="C146" s="10" t="n"/>
       <c r="D146" s="9" t="n"/>
-      <c r="E146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H146" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E146" s="9" t="n"/>
+      <c r="F146" s="9" t="n"/>
+      <c r="G146" s="9" t="n"/>
+      <c r="H146" s="9" t="n"/>
       <c r="I146" s="10" t="n"/>
       <c r="J146" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K146" s="9" t="n"/>
       <c r="L146" s="11" t="n"/>
-      <c r="M146" s="8" t="inlineStr"/>
+      <c r="M146" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t>خام عجينه بقري اسبيشيال</t>
+          <t>خام عجينة برجر  اسبيشيال</t>
         </is>
       </c>
       <c r="B147" s="9" t="n">
@@ -6508,69 +6444,57 @@
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة برجر  الهنا</t>
-        </is>
-      </c>
-      <c r="B148" s="9" t="n">
-        <v>0</v>
-      </c>
+          <t>خاج عجينة كفته اسبيشيال</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="n"/>
       <c r="C148" s="10" t="n"/>
       <c r="D148" s="9" t="n"/>
-      <c r="E148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E148" s="9" t="n"/>
+      <c r="F148" s="9" t="n"/>
+      <c r="G148" s="9" t="n"/>
+      <c r="H148" s="9" t="n"/>
       <c r="I148" s="10" t="n"/>
       <c r="J148" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K148" s="9" t="n"/>
       <c r="L148" s="11" t="n"/>
-      <c r="M148" s="8" t="inlineStr"/>
+      <c r="M148" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة كفته الهنا</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="n">
-        <v>0</v>
-      </c>
+          <t>خام مفروم اسبيشيال</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="n"/>
       <c r="C149" s="10" t="n"/>
       <c r="D149" s="9" t="n"/>
-      <c r="E149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E149" s="9" t="n"/>
+      <c r="F149" s="9" t="n"/>
+      <c r="G149" s="9" t="n"/>
+      <c r="H149" s="9" t="n"/>
       <c r="I149" s="10" t="n"/>
       <c r="J149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K149" s="9" t="n"/>
       <c r="L149" s="11" t="n"/>
-      <c r="M149" s="8" t="inlineStr"/>
+      <c r="M149" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة سجق الهنا</t>
+          <t>خام عجينه بقري اسبيشيال</t>
         </is>
       </c>
       <c r="B150" s="9" t="n">
@@ -6601,38 +6525,32 @@
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>خام عجينة برجر اسبيشيال</t>
-        </is>
-      </c>
-      <c r="B151" s="9" t="n">
-        <v>0</v>
-      </c>
+          <t>خام عجينه مفروم صويا</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="n"/>
       <c r="C151" s="10" t="n"/>
       <c r="D151" s="9" t="n"/>
-      <c r="E151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E151" s="9" t="n"/>
+      <c r="F151" s="9" t="n"/>
+      <c r="G151" s="9" t="n"/>
+      <c r="H151" s="9" t="n"/>
       <c r="I151" s="10" t="n"/>
       <c r="J151" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K151" s="9" t="n"/>
       <c r="L151" s="11" t="n"/>
-      <c r="M151" s="8" t="inlineStr"/>
+      <c r="M151" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>فلتر هواء</t>
+          <t>خام عجينه سجق اسبيشيال</t>
         </is>
       </c>
       <c r="B152" s="9" t="n"/>
@@ -6654,26 +6572,523 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>خام مفروم صويا الهنا</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="n"/>
+      <c r="C153" s="10" t="n"/>
+      <c r="D153" s="9" t="n"/>
+      <c r="E153" s="9" t="n"/>
+      <c r="F153" s="9" t="n"/>
+      <c r="G153" s="9" t="n"/>
+      <c r="H153" s="9" t="n"/>
+      <c r="I153" s="10" t="n"/>
+      <c r="J153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" s="9" t="n"/>
+      <c r="L153" s="11" t="n"/>
+      <c r="M153" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
+    </row>
     <row r="154">
-      <c r="A154" s="12" t="inlineStr">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>خام عجينة برجر الهنا</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" s="10" t="n"/>
+      <c r="D154" s="9" t="n"/>
+      <c r="E154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="10" t="n"/>
+      <c r="J154" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" s="9" t="n"/>
+      <c r="L154" s="11" t="n"/>
+      <c r="M154" s="8" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>خام عجينة كفته الهنا</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" s="10" t="n"/>
+      <c r="D155" s="9" t="n"/>
+      <c r="E155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="10" t="n"/>
+      <c r="J155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" s="9" t="n"/>
+      <c r="L155" s="11" t="n"/>
+      <c r="M155" s="8" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>خام عجينة سجق الهنا</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C156" s="10" t="n"/>
+      <c r="D156" s="9" t="n"/>
+      <c r="E156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="10" t="n"/>
+      <c r="J156" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" s="9" t="n"/>
+      <c r="L156" s="11" t="n"/>
+      <c r="M156" s="8" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>موزة فرخة</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="n"/>
+      <c r="C157" s="10" t="n"/>
+      <c r="D157" s="9" t="n"/>
+      <c r="E157" s="9" t="n"/>
+      <c r="F157" s="9" t="n"/>
+      <c r="G157" s="9" t="n"/>
+      <c r="H157" s="9" t="n"/>
+      <c r="I157" s="10" t="n"/>
+      <c r="J157" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" s="9" t="n"/>
+      <c r="L157" s="11" t="n"/>
+      <c r="M157" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>فلاتر</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" s="10" t="n"/>
+      <c r="D158" s="9" t="n"/>
+      <c r="E158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="10" t="n"/>
+      <c r="J158" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K158" s="9" t="n"/>
+      <c r="L158" s="11" t="n"/>
+      <c r="M158" s="8" t="inlineStr">
+        <is>
+          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>استطوانة فريون</t>
+        </is>
+      </c>
+      <c r="B159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C159" s="10" t="n"/>
+      <c r="D159" s="9" t="n"/>
+      <c r="E159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="10" t="n"/>
+      <c r="J159" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" s="9" t="n"/>
+      <c r="L159" s="11" t="n"/>
+      <c r="M159" s="8" t="inlineStr">
+        <is>
+          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>فلتر خاص بالثلاجة</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C160" s="10" t="n"/>
+      <c r="D160" s="9" t="n"/>
+      <c r="E160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="10" t="n"/>
+      <c r="J160" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" s="9" t="n"/>
+      <c r="L160" s="11" t="n"/>
+      <c r="M160" s="8" t="inlineStr">
+        <is>
+          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>زيت سيارات</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C161" s="6" t="n"/>
+      <c r="D161" s="5" t="n"/>
+      <c r="E161" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I161" s="6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J161" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>21600</v>
+      </c>
+      <c r="L161" s="7" t="n"/>
+      <c r="M161" s="4" t="inlineStr">
+        <is>
+          <t>الوحدة: عبوة 5 كجم (سعر العبوة وليس الكجم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>فلتر هواء دبابة</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="n"/>
+      <c r="C162" s="10" t="n"/>
+      <c r="D162" s="9" t="n"/>
+      <c r="E162" s="9" t="n"/>
+      <c r="F162" s="9" t="n"/>
+      <c r="G162" s="9" t="n"/>
+      <c r="H162" s="9" t="n"/>
+      <c r="I162" s="10" t="n"/>
+      <c r="J162" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K162" s="9" t="n"/>
+      <c r="L162" s="11" t="n"/>
+      <c r="M162" s="8" t="inlineStr">
+        <is>
+          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>ماجي</t>
+        </is>
+      </c>
+      <c r="B163" s="9" t="n"/>
+      <c r="C163" s="10" t="n"/>
+      <c r="D163" s="9" t="n"/>
+      <c r="E163" s="9" t="n"/>
+      <c r="F163" s="9" t="n"/>
+      <c r="G163" s="9" t="n"/>
+      <c r="H163" s="9" t="n"/>
+      <c r="I163" s="10" t="n"/>
+      <c r="J163" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" s="9" t="n"/>
+      <c r="L163" s="11" t="n"/>
+      <c r="M163" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>حشوة زيت</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" s="10" t="n"/>
+      <c r="D164" s="9" t="n"/>
+      <c r="E164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="10" t="n"/>
+      <c r="J164" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K164" s="9" t="n"/>
+      <c r="L164" s="11" t="n"/>
+      <c r="M164" s="8" t="inlineStr">
+        <is>
+          <t>صنف بلا سعر مُثبت (غير مُسعّر فى يوليو ولا مشتريات له فى أغسطس) — يلزم إدخال سعر لتقييمه</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>خلطة استربس 10</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="n"/>
+      <c r="C165" s="10" t="n"/>
+      <c r="D165" s="9" t="n"/>
+      <c r="E165" s="9" t="n"/>
+      <c r="F165" s="9" t="n"/>
+      <c r="G165" s="9" t="n"/>
+      <c r="H165" s="9" t="n"/>
+      <c r="I165" s="10" t="n"/>
+      <c r="J165" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" s="9" t="n"/>
+      <c r="L165" s="11" t="n"/>
+      <c r="M165" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="8" t="inlineStr">
+        <is>
+          <t>خلطة استربس 20</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="n"/>
+      <c r="C166" s="10" t="n"/>
+      <c r="D166" s="9" t="n"/>
+      <c r="E166" s="9" t="n"/>
+      <c r="F166" s="9" t="n"/>
+      <c r="G166" s="9" t="n"/>
+      <c r="H166" s="9" t="n"/>
+      <c r="I166" s="10" t="n"/>
+      <c r="J166" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="9" t="n"/>
+      <c r="L166" s="11" t="n"/>
+      <c r="M166" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>خلطة استربس 30</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="n"/>
+      <c r="C167" s="10" t="n"/>
+      <c r="D167" s="9" t="n"/>
+      <c r="E167" s="9" t="n"/>
+      <c r="F167" s="9" t="n"/>
+      <c r="G167" s="9" t="n"/>
+      <c r="H167" s="9" t="n"/>
+      <c r="I167" s="10" t="n"/>
+      <c r="J167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" s="9" t="n"/>
+      <c r="L167" s="11" t="n"/>
+      <c r="M167" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>خلطة بانيه A</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="n"/>
+      <c r="C168" s="10" t="n"/>
+      <c r="D168" s="9" t="n"/>
+      <c r="E168" s="9" t="n"/>
+      <c r="F168" s="9" t="n"/>
+      <c r="G168" s="9" t="n"/>
+      <c r="H168" s="9" t="n"/>
+      <c r="I168" s="10" t="n"/>
+      <c r="J168" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" s="9" t="n"/>
+      <c r="L168" s="11" t="n"/>
+      <c r="M168" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>خلطة بانيه B</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="10" t="n"/>
+      <c r="D169" s="9" t="n"/>
+      <c r="E169" s="9" t="n"/>
+      <c r="F169" s="9" t="n"/>
+      <c r="G169" s="9" t="n"/>
+      <c r="H169" s="9" t="n"/>
+      <c r="I169" s="10" t="n"/>
+      <c r="J169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" s="9" t="n"/>
+      <c r="L169" s="11" t="n"/>
+      <c r="M169" s="8" t="inlineStr">
+        <is>
+          <t>صنف جديد لم يكن مدرجًا بجرد يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="12" t="inlineStr">
         <is>
           <t>إجمالى قيمة مخزون الخامات آخر أغسطس 2026 (الأصناف المُسعّرة)</t>
         </is>
       </c>
-      <c r="B154" s="12" t="n"/>
-      <c r="C154" s="12" t="n"/>
-      <c r="D154" s="12" t="n"/>
-      <c r="E154" s="12" t="n"/>
-      <c r="F154" s="12" t="n"/>
-      <c r="G154" s="12" t="n"/>
-      <c r="H154" s="12" t="n"/>
-      <c r="I154" s="12" t="n"/>
-      <c r="J154" s="12" t="n"/>
-      <c r="K154" s="12" t="n">
-        <v>2977705.44</v>
-      </c>
-      <c r="L154" s="12" t="n"/>
-      <c r="M154" s="12" t="n"/>
+      <c r="B171" s="12" t="n"/>
+      <c r="C171" s="12" t="n"/>
+      <c r="D171" s="12" t="n"/>
+      <c r="E171" s="12" t="n"/>
+      <c r="F171" s="12" t="n"/>
+      <c r="G171" s="12" t="n"/>
+      <c r="H171" s="12" t="n"/>
+      <c r="I171" s="12" t="n"/>
+      <c r="J171" s="12" t="n"/>
+      <c r="K171" s="12" t="n">
+        <v>2661861.09</v>
+      </c>
+      <c r="L171" s="12" t="n"/>
+      <c r="M171" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7159,7 +7574,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>فلانك</t>
+          <t>فلانك + مجمل رصيد اللحمة بالنفق</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -15611,7 +16026,7 @@
       <c r="D108" s="17" t="n"/>
       <c r="E108" s="17" t="n"/>
       <c r="F108" s="17" t="n">
-        <v>3413305.73</v>
+        <v>3097461.38</v>
       </c>
       <c r="G108" s="17" t="n"/>
     </row>
@@ -15936,7 +16351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -16132,7 +16547,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>كروت كبده شرائح 350</t>
+          <t>كروت كبده علب 350</t>
         </is>
       </c>
       <c r="B20" s="22" t="n">
@@ -16162,7 +16577,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>كروت مفروم صويا ازرق 350</t>
+          <t>كروت استربس</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
@@ -16172,97 +16587,97 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>طبق مسطح 3/4شفاف</t>
+          <t>كروت برجر أبو هاشم</t>
         </is>
       </c>
       <c r="B24" s="22" t="n">
-        <v>827</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>برنيك برجر</t>
+          <t>طبق مسطح 1/2 شفاف</t>
         </is>
       </c>
       <c r="B25" s="22" t="n">
-        <v>442</v>
+        <v>827</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>برنيك سجق</t>
+          <t>برانيك صويا</t>
         </is>
       </c>
       <c r="B26" s="22" t="n">
-        <v>258</v>
+        <v>442</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>أكياس استربس اسبيشيال ص</t>
+          <t>طبق مسطح 1 ك شفاف</t>
         </is>
       </c>
       <c r="B27" s="22" t="n">
-        <v>82</v>
+        <v>379</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>طبق مسطح 1/2 شفاف</t>
+          <t>برنيك برجر</t>
         </is>
       </c>
       <c r="B28" s="22" t="n">
-        <v>14</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>فلاتر</t>
+          <t>أكياس استربس اسبيشيال ص</t>
         </is>
       </c>
       <c r="B29" s="22" t="n">
-        <v>9</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>حشوة زيت</t>
+          <t>فلاتر</t>
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>مذيب</t>
+          <t>فلتر هواء دبابة</t>
         </is>
       </c>
       <c r="B31" s="22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>مزيل لماكينة التغليف</t>
+          <t>حشوة زيت</t>
         </is>
       </c>
       <c r="B32" s="22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>استطوانة فريون</t>
+          <t>مزيل لماكينة التغليف</t>
         </is>
       </c>
       <c r="B33" s="22" t="n">
@@ -16272,10 +16687,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>استطوانة فريون</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>فلتر خاص بالثلاجة</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B35" s="22" t="n">
         <v>1</v>
       </c>
     </row>

--- a/تسعير جرد اخر شهر ٨ سنة ٢٠٢٦.xlsx
+++ b/تسعير جرد اخر شهر ٨ سنة ٢٠٢٦.xlsx
@@ -14790,36 +14790,40 @@
         <v>44.95</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>44.95</v>
+        <v>49.1199</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>21710.85</v>
+        <v>23724.91</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>خارج نطاق الوصفات التسع — سعر يوليو مُبقًى دون تحديث</t>
+          <t>من «خلطة بانيه 28-8-2026.pdf»: 51.86862 × 0.8 كجم = 41.4949 + تغليف 6.25 + عمولة 1.375</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>بانيه 900</t>
         </is>
       </c>
-      <c r="B49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>بلا سعر — خارج نطاق الوصفات ولم يُسعَّر من قبل</t>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n">
+        <v>54.4318</v>
+      </c>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>من «خلطة بانيه 28-8-2026.pdf»: 51.86862 × 0.9 كجم = 46.6818 + تغليف 6.25 + عمولة 1.5 | صنف لم يكن مُسعّرًا من قبل</t>
         </is>
       </c>
     </row>
@@ -14944,17 +14948,17 @@
         <v>136</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>136</v>
+        <v>130.7381</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>1904</v>
+        <v>1830.33</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>خارج نطاق الوصفات التسع — سعر يوليو مُبقًى دون تحديث</t>
+          <t>من «خلطه استربس 28-8-2026.pdf»: 137.12570 × 0.9 كجم = 123.4131 + تغليف 3.2 + عمولة 4.125</t>
         </is>
       </c>
     </row>
@@ -15152,55 +15156,63 @@
         <v>58.35</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>58.35</v>
+        <v>54.4318</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>2100.6</v>
+        <v>1959.54</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>خارج نطاق الوصفات التسع — سعر يوليو مُبقًى دون تحديث</t>
+          <t>من «خلطة بانيه 28-8-2026.pdf»: 51.86862 × 0.9 كجم = 46.6818 + تغليف 6.25 + عمولة 1.5</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>بانيه اسبيشيال 800</t>
         </is>
       </c>
-      <c r="B63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="10" t="n"/>
-      <c r="D63" s="10" t="n"/>
-      <c r="E63" s="11" t="n"/>
-      <c r="F63" s="9" t="n"/>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>بلا سعر — خارج نطاق الوصفات ولم يُسعَّر من قبل</t>
+      <c r="B63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n">
+        <v>49.1199</v>
+      </c>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>من «خلطة بانيه 28-8-2026.pdf»: 51.86862 × 0.8 كجم = 41.4949 + تغليف 6.25 + عمولة 1.375 | صنف لم يكن مُسعّرًا من قبل</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>بانيه اسبيشيال حار800</t>
         </is>
       </c>
-      <c r="B64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="10" t="n"/>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="11" t="n"/>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>بلا سعر — خارج نطاق الوصفات ولم يُسعَّر من قبل</t>
+      <c r="B64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n">
+        <v>49.1199</v>
+      </c>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>من «خلطة بانيه 28-8-2026.pdf»: 51.86862 × 0.8 كجم = 41.4949 + تغليف 6.25 + عمولة 1.375 | صنف لم يكن مُسعّرًا من قبل</t>
         </is>
       </c>
     </row>
@@ -15963,40 +15975,48 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>بانيه 1 ك</t>
         </is>
       </c>
-      <c r="B103" s="9" t="n">
+      <c r="B103" s="5" t="n">
         <v>1091</v>
       </c>
-      <c r="C103" s="10" t="n"/>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="11" t="n"/>
-      <c r="F103" s="9" t="n"/>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>بلا سعر — خارج نطاق الوصفات ولم يُسعَّر من قبل</t>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n">
+        <v>51.8686</v>
+      </c>
+      <c r="E103" s="7" t="n"/>
+      <c r="F103" s="5" t="n">
+        <v>56588.64</v>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>سعر كيلو الخلطة كما هو بملف «خلطة بانيه 28-8-2026.pdf» (بلا تغليف أو عمولة) | صنف لم يكن مُسعّرًا من قبل</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>استربس 1 ك</t>
         </is>
       </c>
-      <c r="B104" s="9" t="n">
+      <c r="B104" s="5" t="n">
         <v>1090</v>
       </c>
-      <c r="C104" s="10" t="n"/>
-      <c r="D104" s="10" t="n"/>
-      <c r="E104" s="11" t="n"/>
-      <c r="F104" s="9" t="n"/>
-      <c r="G104" s="8" t="inlineStr">
-        <is>
-          <t>بلا سعر — خارج نطاق الوصفات ولم يُسعَّر من قبل</t>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n">
+        <v>137.1257</v>
+      </c>
+      <c r="E104" s="7" t="n"/>
+      <c r="F104" s="5" t="n">
+        <v>149467.01</v>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>سعر كيلو الخلطة كما هو بملف «خلطه استربس 28-8-2026.pdf» (بلا تغليف أو عمولة) | صنف لم يكن مُسعّرًا من قبل</t>
         </is>
       </c>
     </row>
@@ -16011,7 +16031,7 @@
       <c r="D106" s="12" t="n"/>
       <c r="E106" s="12" t="n"/>
       <c r="F106" s="12" t="n">
-        <v>435600.29</v>
+        <v>643455.27</v>
       </c>
       <c r="G106" s="12" t="n"/>
     </row>
@@ -16026,7 +16046,7 @@
       <c r="D108" s="17" t="n"/>
       <c r="E108" s="17" t="n"/>
       <c r="F108" s="17" t="n">
-        <v>3097461.38</v>
+        <v>3305316.36</v>
       </c>
       <c r="G108" s="17" t="n"/>
     </row>
@@ -16351,7 +16371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -16477,117 +16497,119 @@
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>المنتج التام</t>
+          <t>البانيه والاستربس</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>أُعيد اشتقاق سعر كل SKU من نفس وصفات التصنيع، باستبدال أسعار الخامات فقط، مع الإبقاء على الكميات ومعاملات الإنتاجية وتكاليف التعبئة دون تغيير.</t>
+          <t>صنفان خارج وصفات التصنيع التسع. أُخذت تكلفتهما من ملفَّى «خلطة بانيه 28-8-2026.pdf» و«خلطه استربس 28-8-2026.pdf» المؤرَّخين 28/08/2026 ⇒ أسعارهما أسعار أغسطس. عبوتا الكيلو سُعِّرتا بسعر كيلو الخلطة كما هو بالملف دون استقراء تغليف أو عمولة، والأوزان 800 و900 جرام بسعرها المُفصَّل بالملف (خلطة + تغليف + عمولة). الأوزان غير الواردة بالملفين (700 جم، 5 كجم، GB 2، بارد دوفا، استبربس 800) تُركت دون استقراء.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
+          <t>المنتج التام</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>أُعيد اشتقاق سعر كل SKU من نفس وصفات التصنيع، باستبدال أسعار الخامات فقط، مع الإبقاء على الكميات ومعاملات الإنتاجية وتكاليف التعبئة دون تغيير.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
           <t>خارج النطاق</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>الأسعار تمثل تكلفة الخامات المباشرة (+ التعبئة للمنتج التام) ولا تشمل الأجور المباشرة ولا الأعباء الصناعية غير المباشرة.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>بنود مشتراة بلا مقابل فى الجرد (لم تدخل التقييم)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>الصنف</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>القيمة (ج.م)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>السبب</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>ببريكا مدخنه</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B18" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>بابريكا مدخّنة صنف مستقل (كود 453) يختلف عن «بابريكا» العادية (كود 84) — لم يُدمج معها تفاديًا لخلط خامتين؛ القيمة 90 ج.م</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>أصناف بالجرد آخر أغسطس برصيد بلا سعر</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>كروت كبده علب 350</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>14451</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>كروت مفروم صافي 350</t>
+          <t>كروت كبده علب 350</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>9225</v>
+        <v>14451</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>كروت مفروم صويا 350</t>
+          <t>كروت مفروم صافي 350</t>
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>8786</v>
+        <v>9225</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>كروت استربس</t>
+          <t>كروت مفروم صويا 350</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>2000</v>
+        <v>8786</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>كروت برجر أبو هاشم</t>
+          <t>كروت استربس</t>
         </is>
       </c>
       <c r="B24" s="22" t="n">
@@ -16597,77 +16619,77 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>طبق مسطح 1/2 شفاف</t>
+          <t>كروت برجر أبو هاشم</t>
         </is>
       </c>
       <c r="B25" s="22" t="n">
-        <v>827</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>برانيك صويا</t>
+          <t>طبق مسطح 1/2 شفاف</t>
         </is>
       </c>
       <c r="B26" s="22" t="n">
-        <v>442</v>
+        <v>827</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>طبق مسطح 1 ك شفاف</t>
+          <t>برانيك صويا</t>
         </is>
       </c>
       <c r="B27" s="22" t="n">
-        <v>379</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>برنيك برجر</t>
+          <t>طبق مسطح 1 ك شفاف</t>
         </is>
       </c>
       <c r="B28" s="22" t="n">
-        <v>258</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>أكياس استربس اسبيشيال ص</t>
+          <t>برنيك برجر</t>
         </is>
       </c>
       <c r="B29" s="22" t="n">
-        <v>82.5</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>فلاتر</t>
+          <t>أكياس استربس اسبيشيال ص</t>
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>9</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>فلتر هواء دبابة</t>
+          <t>فلاتر</t>
         </is>
       </c>
       <c r="B31" s="22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>حشوة زيت</t>
+          <t>فلتر هواء دبابة</t>
         </is>
       </c>
       <c r="B32" s="22" t="n">
@@ -16677,17 +16699,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>مزيل لماكينة التغليف</t>
+          <t>حشوة زيت</t>
         </is>
       </c>
       <c r="B33" s="22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>استطوانة فريون</t>
+          <t>مزيل لماكينة التغليف</t>
         </is>
       </c>
       <c r="B34" s="22" t="n">
@@ -16697,10 +16719,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>استطوانة فريون</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>فلتر خاص بالثلاجة</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B36" s="22" t="n">
         <v>1</v>
       </c>
     </row>

--- a/تسعير جرد اخر شهر ٨ سنة ٢٠٢٦.xlsx
+++ b/تسعير جرد اخر شهر ٨ سنة ٢٠٢٦.xlsx
@@ -28702,7 +28702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -28857,27 +28857,6 @@
       <c r="E8" s="16">
         <f>IF(ABS(D8)&lt;=0,"✔ مطابق","✘ فرق")</f>
         <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>أسعار ملف جرد آخر سبتمبر = متوسط أغسطس المحسوب مستقلًا (فحص عبر الملفين بالسكربت)</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>149</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>149</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>✔ مطابق</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -29042,12 +29021,12 @@
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>ملف سبتمبر</t>
+          <t>سبتمبر</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>«تسعير جرد اخر شهر ٩ سنة ٢٠٢٦.xlsx» بنفس شكل ملفات الجرد؛ السعر = متوسط أغسطس والكميات فارغة للتعبئة. لا توجد مشتريات سبتمبر بالمستودع؛ عند توفرها يُعاد احتساب متوسط سبتمبر بنفس المعادلة.</t>
+          <t>تقييم جرد آخر سبتمبر فى «model/wac_september_2026.py» (رصيد أول المدة = جرد 31/8 × متوسط أغسطس + مشتريات سبتمبر).</t>
         </is>
       </c>
       <c r="C13" s="24" t="n"/>
